--- a/output/exports/intraday.xlsx
+++ b/output/exports/intraday.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT95"/>
+  <dimension ref="A1:BJ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>ATR_Percent</t>
+          <t>ATR_Pct</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -629,20 +629,100 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>entry_low</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>entry_high</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>entry_price</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>target_1</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>target_2</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>risk_points</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>reward_1_points</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>reward_2_points</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>risk_reward_1</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>risk_reward_2</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>trade_plan_type</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>trade_plan_status</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>trade_plan_reason</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>invalidation</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
           <t>risk_reward</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>setup_reasons</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>trade_plan_quality</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
         <is>
           <t>technical_rank</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
@@ -788,17 +868,75 @@
         <v>87</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.2771079076843177</v>
-      </c>
-      <c r="AR2" t="inlineStr">
+        <v>24.04</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Below ₹23.48</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS2" t="n">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI2" t="n">
         <v>1</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BJ2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -942,17 +1080,75 @@
         <v>86</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.2369478742252832</v>
-      </c>
-      <c r="AR3" t="inlineStr">
+        <v>18.09</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>Below ₹17.09</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG3" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS3" t="n">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI3" t="n">
         <v>2</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BJ3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1096,17 +1292,75 @@
         <v>86</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.1860642598434397</v>
-      </c>
-      <c r="AR4" t="inlineStr">
+        <v>1849.47</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1871.57</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1849.47</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1776.86</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1975.76</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2070.47</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>126.29</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>221</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>Below ₹1776.86</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG4" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS4" t="n">
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI4" t="n">
         <v>2</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BJ4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1250,17 +1504,75 @@
         <v>86</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.07027007800283061</v>
-      </c>
-      <c r="AR5" t="inlineStr">
+        <v>21.19</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>Below ₹19.71</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG5" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS5" t="n">
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI5" t="n">
         <v>2</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BJ5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1404,17 +1716,75 @@
         <v>86</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.1334990530806877</v>
-      </c>
-      <c r="AR6" t="inlineStr">
+        <v>2332.35</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2363.51</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2332.35</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2229.98</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2510.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2643.93</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>178.04</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>311.58</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>Below ₹2229.98</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG6" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS6" t="n">
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI6" t="n">
         <v>2</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BJ6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1558,17 +1928,75 @@
         <v>84</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.01704771553404366</v>
-      </c>
-      <c r="AR7" t="inlineStr">
+        <v>931.4299999999999</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>944.09</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>931.4299999999999</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>889.8200000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1003.78</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1058.05</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>126.63</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>Below ₹889.82</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG7" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS7" t="n">
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI7" t="n">
         <v>6</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BJ7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1712,17 +2140,75 @@
         <v>84</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.02758682377949483</v>
-      </c>
-      <c r="AR8" t="inlineStr">
+        <v>16.94</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>Below ₹16.29</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG8" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS8" t="n">
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI8" t="n">
         <v>6</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BJ8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1866,17 +2352,75 @@
         <v>84</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.07843126255203133</v>
-      </c>
-      <c r="AR9" t="inlineStr">
+        <v>8.51</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>Below ₹8.13</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG9" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS9" t="n">
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI9" t="n">
         <v>13</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BJ9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2020,17 +2564,75 @@
         <v>84</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.1368307193077339</v>
-      </c>
-      <c r="AR10" t="inlineStr">
+        <v>8655.27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8891.120000000001</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8812.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8419.42</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9362.809999999999</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9755.889999999999</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>550.3099999999999</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>943.39</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>Below ₹8419.42</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG10" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS10" t="n">
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI10" t="n">
         <v>13</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BJ10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2174,17 +2776,75 @@
         <v>83</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.09510595881980327</v>
-      </c>
-      <c r="AR11" t="inlineStr">
+        <v>508.62</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>517.78</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>508.62</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>478.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>561</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>600.28</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>Below ₹478.50</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG11" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS11" t="n">
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI11" t="n">
         <v>8</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BJ11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2328,17 +2988,75 @@
         <v>82</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.08296455835829694</v>
-      </c>
-      <c r="AR12" t="inlineStr">
+        <v>139.93</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>141.29</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>139.93</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>135.46</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>153.52</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>Below ₹135.46</t>
+        </is>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG12" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS12" t="n">
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI12" t="n">
         <v>9</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BJ12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2482,17 +3200,75 @@
         <v>82</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.07410272783592398</v>
-      </c>
-      <c r="AR13" t="inlineStr">
+        <v>217.63</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>220.04</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>217.63</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>209.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>231.42</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>241.77</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>Below ₹209.70</t>
+        </is>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG13" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
-      <c r="AS13" t="n">
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI13" t="n">
         <v>9</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BJ13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2628,17 +3404,75 @@
         <v>82</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.227752325017907</v>
-      </c>
-      <c r="AR14" t="inlineStr">
+        <v>142.61</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>142.61</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>153.94</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>162.44</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>Below ₹136.10</t>
+        </is>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG14" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS14" t="n">
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI14" t="n">
         <v>9</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BJ14" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2782,17 +3616,75 @@
         <v>82</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.1984485748272413</v>
-      </c>
-      <c r="AR15" t="inlineStr">
+        <v>72</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>72</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>66.81999999999999</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>87.77</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>Below ₹66.82</t>
+        </is>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG15" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS15" t="n">
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI15" t="n">
         <v>9</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BJ15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2936,17 +3828,75 @@
         <v>82</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.6662873839712555</v>
-      </c>
-      <c r="AR16" t="inlineStr">
+        <v>3126.29</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3169.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3155.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3083.08</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3255.92</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3327.94</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>100.82</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>172.84</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>Below ₹3083.08</t>
+        </is>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG16" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
-      <c r="AS16" t="n">
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI16" t="n">
         <v>24</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BJ16" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3090,17 +4040,75 @@
         <v>82</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.1936507936507937</v>
-      </c>
-      <c r="AR17" t="inlineStr">
+        <v>930.09</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>950.58</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>943.75</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>909.61</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>991.54</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1025.68</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>81.93000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>Below ₹909.61</t>
+        </is>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG17" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS17" t="n">
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI17" t="n">
         <v>24</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BJ17" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3244,17 +4252,75 @@
         <v>81</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.08616775730105113</v>
-      </c>
-      <c r="AR18" t="inlineStr">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>64</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>82.94</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>Below ₹64.00</t>
+        </is>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG18" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS18" t="n">
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI18" t="n">
         <v>13</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BJ18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3398,17 +4464,75 @@
         <v>81</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0.1202894372010538</v>
-      </c>
-      <c r="AR19" t="inlineStr">
+        <v>396.16</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>402.71</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>396.16</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>433.59</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>461.66</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>Below ₹374.64</t>
+        </is>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG19" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS19" t="n">
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI19" t="n">
         <v>13</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BJ19" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3552,17 +4676,75 @@
         <v>81</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.02226869822683754</v>
-      </c>
-      <c r="AR20" t="inlineStr">
+        <v>399.67</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>405.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>399.67</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>433.54</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>458.93</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>Below ₹380.20</t>
+        </is>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG20" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS20" t="n">
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI20" t="n">
         <v>13</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BJ20" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3706,17 +4888,75 @@
         <v>81</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.206133018539621</v>
-      </c>
-      <c r="AR21" t="inlineStr">
+        <v>26.22</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>Below ₹24.81</t>
+        </is>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG21" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS21" t="n">
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI21" t="n">
         <v>13</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BJ21" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3860,17 +5100,75 @@
         <v>81</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.03697762763578034</v>
-      </c>
-      <c r="AR22" t="inlineStr">
+        <v>918.75</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>927.86</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>918.75</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>888.8200000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>970.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1009.84</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>Below ₹888.82</t>
+        </is>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG22" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS22" t="n">
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI22" t="n">
         <v>13</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="BJ22" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4014,17 +5312,75 @@
         <v>81</v>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.04000019929846939</v>
-      </c>
-      <c r="AR23" t="inlineStr">
+        <v>741.77</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>750.58</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>741.77</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>712.84</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>792.1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>829.84</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>88.06</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>Below ₹712.84</t>
+        </is>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG23" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS23" t="n">
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI23" t="n">
         <v>13</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="BJ23" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4168,17 +5524,75 @@
         <v>81</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.2068142407819016</v>
-      </c>
-      <c r="AR24" t="inlineStr">
+        <v>1859.21</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1890.4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1859.21</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1756.7</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2037.48</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2171.18</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>102.51</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>178.27</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>311.98</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>Below ₹1756.70</t>
+        </is>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG24" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS24" t="n">
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI24" t="n">
         <v>13</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="BJ24" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4322,17 +5736,75 @@
         <v>81</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.07811447811447811</v>
-      </c>
-      <c r="AR25" t="inlineStr">
+        <v>11890.39</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>12200.3</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>12097</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>11580.48</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>12820.12</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>13336.64</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>516.52</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>723.12</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1239.64</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>Below ₹11580.48</t>
+        </is>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG25" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS25" t="n">
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI25" t="n">
         <v>30</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="BJ25" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4476,17 +5948,75 @@
         <v>81</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.02105263157894737</v>
-      </c>
-      <c r="AR26" t="inlineStr">
+        <v>1390.88</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1440.56</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1424</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1341.2</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1539.93</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1622.73</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>115.93</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>198.73</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>Below ₹1341.20</t>
+        </is>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG26" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS26" t="n">
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI26" t="n">
         <v>30</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="BJ26" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4630,17 +6160,75 @@
         <v>81</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.04560891802842767</v>
-      </c>
-      <c r="AR27" t="inlineStr">
+        <v>521.78</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>528.28</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>521.78</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>500.45</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>558.89</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>586.72</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>Below ₹500.45</t>
+        </is>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG27" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS27" t="n">
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI27" t="n">
         <v>41</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="BJ27" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4784,17 +6372,75 @@
         <v>80</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.008398738472959138</v>
-      </c>
-      <c r="AR28" t="inlineStr">
+        <v>91.62</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>108.42</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>Below ₹86.10</t>
+        </is>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG28" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS28" t="n">
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI28" t="n">
         <v>22</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="BJ28" t="n">
         <v>27</v>
       </c>
     </row>
@@ -4938,17 +6584,75 @@
         <v>80</v>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.06898572389981884</v>
-      </c>
-      <c r="AR29" t="inlineStr">
+        <v>818.3</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>831.13</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>818.3</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>776.14</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>891.61</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>946.6</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>73.31</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>Below ₹776.14</t>
+        </is>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG29" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS29" t="n">
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI29" t="n">
         <v>22</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="BJ29" t="n">
         <v>27</v>
       </c>
     </row>
@@ -5092,17 +6796,75 @@
         <v>79</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.09197321598528624</v>
-      </c>
-      <c r="AR30" t="inlineStr">
+        <v>1150.14</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1162.39</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1150.14</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1109.9</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1220.13</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1272.62</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
+        <is>
+          <t>Below ₹1109.90</t>
+        </is>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG30" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS30" t="n">
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI30" t="n">
         <v>24</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="BJ30" t="n">
         <v>29</v>
       </c>
     </row>
@@ -5238,17 +7000,75 @@
         <v>79</v>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.03475533382765713</v>
-      </c>
-      <c r="AR31" t="inlineStr">
+        <v>357.88</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>361.49</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>357.88</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>346</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>378.54</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>394.03</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>Below ₹346.00</t>
+        </is>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG31" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS31" t="n">
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI31" t="n">
         <v>24</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="BJ31" t="n">
         <v>29</v>
       </c>
     </row>
@@ -5392,17 +7212,75 @@
         <v>79</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-0.2041114926679397</v>
-      </c>
-      <c r="AR32" t="inlineStr">
+        <v>435.87</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>441.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>435.87</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>417.4</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>468</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>Below ₹417.40</t>
+        </is>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG32" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS32" t="n">
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI32" t="n">
         <v>24</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="BJ32" t="n">
         <v>29</v>
       </c>
     </row>
@@ -5546,17 +7424,75 @@
         <v>79</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-0.138098311939258</v>
-      </c>
-      <c r="AR33" t="inlineStr">
+        <v>1810.07</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1833.55</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1810.07</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1732.89</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1944.28</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2044.94</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>77.17</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>134.21</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>234.88</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>Below ₹1732.89</t>
+        </is>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG33" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS33" t="n">
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI33" t="n">
         <v>24</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="BJ33" t="n">
         <v>29</v>
       </c>
     </row>
@@ -5700,17 +7636,75 @@
         <v>79</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.06417567815476456</v>
-      </c>
-      <c r="AR34" t="inlineStr">
+        <v>541.46</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>555.84</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>551.05</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>527.09</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>584.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>608.5599999999999</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
+        <is>
+          <t>Below ₹527.09</t>
+        </is>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG34" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS34" t="n">
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI34" t="n">
         <v>41</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="BJ34" t="n">
         <v>29</v>
       </c>
     </row>
@@ -5854,17 +7848,75 @@
         <v>78</v>
       </c>
       <c r="AQ35" t="n">
-        <v>-0.07684679753063332</v>
-      </c>
-      <c r="AR35" t="inlineStr">
+        <v>422</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>427.38</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>422</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>404.35</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>452.7</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>475.73</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>Below ₹404.35</t>
+        </is>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG35" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS35" t="n">
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI35" t="n">
         <v>30</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="BJ35" t="n">
         <v>34</v>
       </c>
     </row>
@@ -6008,17 +8060,75 @@
         <v>78</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.04112183090928875</v>
-      </c>
-      <c r="AR36" t="inlineStr">
+        <v>242.2</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>245.45</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>260.8</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>274.76</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>Below ₹231.50</t>
+        </is>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG36" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS36" t="n">
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI36" t="n">
         <v>45</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="BJ36" t="n">
         <v>34</v>
       </c>
     </row>
@@ -6162,17 +8272,75 @@
         <v>77</v>
       </c>
       <c r="AQ37" t="n">
-        <v>-0.2870200899278381</v>
-      </c>
-      <c r="AR37" t="inlineStr">
+        <v>20.13</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>Below ₹19.14</t>
+        </is>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG37" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS37" t="n">
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI37" t="n">
         <v>33</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="BJ37" t="n">
         <v>38</v>
       </c>
     </row>
@@ -6316,17 +8484,75 @@
         <v>77</v>
       </c>
       <c r="AQ38" t="n">
-        <v>-0.3125889907289262</v>
-      </c>
-      <c r="AR38" t="inlineStr">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>Below ₹68.42</t>
+        </is>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG38" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS38" t="n">
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI38" t="n">
         <v>33</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="BJ38" t="n">
         <v>38</v>
       </c>
     </row>
@@ -6462,17 +8688,75 @@
         <v>77</v>
       </c>
       <c r="AQ39" t="n">
-        <v>-0.5411091037639973</v>
-      </c>
-      <c r="AR39" t="inlineStr">
+        <v>213.09</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>216.41</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>213.09</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>202.17</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>232.07</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>246.31</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>Below ₹202.17</t>
+        </is>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG39" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS39" t="n">
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI39" t="n">
         <v>33</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="BJ39" t="n">
         <v>38</v>
       </c>
     </row>
@@ -6616,17 +8900,75 @@
         <v>77</v>
       </c>
       <c r="AQ40" t="n">
-        <v>-0.3415007451803956</v>
-      </c>
-      <c r="AR40" t="inlineStr">
+        <v>1032.48</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1051.08</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1032.48</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>971.33</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1138.81</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1218.56</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>106.34</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>186.09</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>Below ₹971.33</t>
+        </is>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG40" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS40" t="n">
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI40" t="n">
         <v>33</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="BJ40" t="n">
         <v>38</v>
       </c>
     </row>
@@ -6770,17 +9112,75 @@
         <v>77</v>
       </c>
       <c r="AQ41" t="n">
-        <v>-0.1264204545454546</v>
-      </c>
-      <c r="AR41" t="inlineStr">
+        <v>492.72</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>500.2</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>492.72</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>468.15</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>535.45</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>567.49</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>74.78</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>Below ₹468.15</t>
+        </is>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG41" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS41" t="n">
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI41" t="n">
         <v>33</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="BJ41" t="n">
         <v>38</v>
       </c>
     </row>
@@ -6924,17 +9324,75 @@
         <v>77</v>
       </c>
       <c r="AQ42" t="n">
-        <v>-0.1479690512532134</v>
-      </c>
-      <c r="AR42" t="inlineStr">
+        <v>3182.1</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>3230.68</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>3182.1</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3022.5</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3459.67</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3667.85</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>277.57</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>485.75</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>Below ₹3022.50</t>
+        </is>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG42" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS42" t="n">
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI42" t="n">
         <v>33</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="BJ42" t="n">
         <v>38</v>
       </c>
     </row>
@@ -7078,17 +9536,75 @@
         <v>77</v>
       </c>
       <c r="AQ43" t="n">
-        <v>-0.1449998450278989</v>
-      </c>
-      <c r="AR43" t="inlineStr">
+        <v>38.25</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>Below ₹36.60</t>
+        </is>
+      </c>
+      <c r="BF43" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG43" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS43" t="n">
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI43" t="n">
         <v>33</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="BJ43" t="n">
         <v>38</v>
       </c>
     </row>
@@ -7232,17 +9748,75 @@
         <v>77</v>
       </c>
       <c r="AQ44" t="n">
-        <v>-0.1685290987967586</v>
-      </c>
-      <c r="AR44" t="inlineStr">
+        <v>399.63</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>405.76</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>399.63</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>434.68</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>460.97</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE44" t="inlineStr">
+        <is>
+          <t>Below ₹379.48</t>
+        </is>
+      </c>
+      <c r="BF44" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG44" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS44" t="n">
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI44" t="n">
         <v>33</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="BJ44" t="n">
         <v>38</v>
       </c>
     </row>
@@ -7386,17 +9960,75 @@
         <v>77</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.1011613601073889</v>
-      </c>
-      <c r="AR45" t="inlineStr">
+        <v>234.73</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>238.77</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>234.73</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>221.45</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>257.83</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>Below ₹221.45</t>
+        </is>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG45" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS45" t="n">
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI45" t="n">
         <v>54</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="BJ45" t="n">
         <v>38</v>
       </c>
     </row>
@@ -7540,17 +10172,75 @@
         <v>76</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.01825662364252532</v>
-      </c>
-      <c r="AR46" t="inlineStr">
+        <v>888.48</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>919.11</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>908.9</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>857.85</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>980.38</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1031.43</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>122.53</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
+        <is>
+          <t>Below ₹857.85</t>
+        </is>
+      </c>
+      <c r="BF46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG46" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS46" t="n">
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI46" t="n">
         <v>45</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="BJ46" t="n">
         <v>48</v>
       </c>
     </row>
@@ -7694,17 +10384,75 @@
         <v>76</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.1517857979146887</v>
-      </c>
-      <c r="AR47" t="inlineStr">
+        <v>11.91</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>Below ₹11.76</t>
+        </is>
+      </c>
+      <c r="BF47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG47" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS47" t="n">
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI47" t="n">
         <v>45</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="BJ47" t="n">
         <v>48</v>
       </c>
     </row>
@@ -7848,17 +10596,75 @@
         <v>76</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.078198022240991</v>
-      </c>
-      <c r="AR48" t="inlineStr">
+        <v>3772.51</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>3856.19</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>3828.3</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>3688.84</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>4023.55</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>4163.01</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>139.46</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>195.25</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>334.71</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
+        <is>
+          <t>Below ₹3688.84</t>
+        </is>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG48" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS48" t="n">
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI48" t="n">
         <v>45</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="BJ48" t="n">
         <v>48</v>
       </c>
     </row>
@@ -8002,17 +10808,75 @@
         <v>76</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.06230021591428169</v>
-      </c>
-      <c r="AR49" t="inlineStr">
+        <v>250.24</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>257.83</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>255.3</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>242.64</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>273.03</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>285.69</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE49" t="inlineStr">
+        <is>
+          <t>Below ₹242.64</t>
+        </is>
+      </c>
+      <c r="BF49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG49" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS49" t="n">
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI49" t="n">
         <v>45</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="BJ49" t="n">
         <v>48</v>
       </c>
     </row>
@@ -8156,17 +11020,75 @@
         <v>76</v>
       </c>
       <c r="AQ50" t="n">
-        <v>-0.02595494449136814</v>
-      </c>
-      <c r="AR50" t="inlineStr">
+        <v>738.24</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>750.48</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>738.24</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>698.04</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>808.17</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>860.61</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>122.36</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
+        <is>
+          <t>Below ₹698.04</t>
+        </is>
+      </c>
+      <c r="BF50" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG50" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS50" t="n">
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI50" t="n">
         <v>59</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="BJ50" t="n">
         <v>48</v>
       </c>
     </row>
@@ -8310,17 +11232,75 @@
         <v>76</v>
       </c>
       <c r="AQ51" t="n">
-        <v>-0.03036922132176373</v>
-      </c>
-      <c r="AR51" t="inlineStr">
+        <v>216.37</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>219.56</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>216.37</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>205.87</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>234.62</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>248.31</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>31.94</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
+        <is>
+          <t>Below ₹205.87</t>
+        </is>
+      </c>
+      <c r="BF51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG51" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS51" t="n">
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI51" t="n">
         <v>59</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="BJ51" t="n">
         <v>48</v>
       </c>
     </row>
@@ -8464,17 +11444,75 @@
         <v>75</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.1366635564233045</v>
-      </c>
-      <c r="AR52" t="inlineStr">
+        <v>381.53</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>387.42</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>381.53</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>415.22</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>440.49</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr">
+        <is>
+          <t>Below ₹362.15</t>
+        </is>
+      </c>
+      <c r="BF52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG52" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS52" t="n">
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI52" t="n">
         <v>67</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="BJ52" t="n">
         <v>56</v>
       </c>
     </row>
@@ -8618,17 +11656,75 @@
         <v>74</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.2365149694381095</v>
-      </c>
-      <c r="AR53" t="inlineStr">
+        <v>623.34</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>637.08</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>632.5</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>609.6</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>664.5599999999999</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>687.45</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>32.06</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
+        <is>
+          <t>Below ₹609.60</t>
+        </is>
+      </c>
+      <c r="BF53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG53" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Positive momentum | Price is close to resistance | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS53" t="n">
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI53" t="n">
         <v>59</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="BJ53" t="n">
         <v>60</v>
       </c>
     </row>
@@ -8772,17 +11868,75 @@
         <v>74</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.1333332061767578</v>
-      </c>
-      <c r="AR54" t="inlineStr">
+        <v>356.21</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>363</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>346.01</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>403.77</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>Below ₹346.01</t>
+        </is>
+      </c>
+      <c r="BF54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG54" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS54" t="n">
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI54" t="n">
         <v>59</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="BJ54" t="n">
         <v>60</v>
       </c>
     </row>
@@ -8926,17 +12080,75 @@
         <v>74</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.6097567027088719</v>
-      </c>
-      <c r="AR55" t="inlineStr">
+        <v>336.96</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>340.09</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>339.05</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>333.84</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>346.35</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>Below ₹333.84</t>
+        </is>
+      </c>
+      <c r="BF55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG55" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS55" t="n">
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI55" t="n">
         <v>59</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="BJ55" t="n">
         <v>60</v>
       </c>
     </row>
@@ -9080,17 +12292,75 @@
         <v>74</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.007502811346391238</v>
-      </c>
-      <c r="AR56" t="inlineStr">
+        <v>445.48</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>455.78</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>452.35</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>435.18</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>476.39</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>493.56</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
+        <is>
+          <t>Below ₹435.18</t>
+        </is>
+      </c>
+      <c r="BF56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG56" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS56" t="n">
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI56" t="n">
         <v>59</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="BJ56" t="n">
         <v>60</v>
       </c>
     </row>
@@ -9234,17 +12504,75 @@
         <v>74</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.09574949840559019</v>
-      </c>
-      <c r="AR57" t="inlineStr">
+        <v>3284.99</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>3326.85</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>3284.99</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3048.57</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3324.7</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>3492.17</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>236.42</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>207.18</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>200 DMA Recovery</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>Confirmation Required</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>Stock is recovering around the 200 DMA. Confirmation above the recovery level is preferred.</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>Below ₹3048.57</t>
+        </is>
+      </c>
+      <c r="BF57" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BG57" t="inlineStr">
         <is>
           <t>Strong positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
-      <c r="AS57" t="n">
+      <c r="BH57" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI57" t="n">
         <v>82</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="BJ57" t="n">
         <v>60</v>
       </c>
     </row>
@@ -9388,17 +12716,75 @@
         <v>74</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.1760297114049672</v>
-      </c>
-      <c r="AR58" t="inlineStr">
+        <v>422.35</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>428.44</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>422.35</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>394.15</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>444.3</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>468.67</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>200 DMA Recovery</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>Confirmation Required</t>
+        </is>
+      </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>Stock is recovering around the 200 DMA. Confirmation above the recovery level is preferred.</t>
+        </is>
+      </c>
+      <c r="BE58" t="inlineStr">
+        <is>
+          <t>Below ₹394.15</t>
+        </is>
+      </c>
+      <c r="BF58" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BG58" t="inlineStr">
         <is>
           <t>Strong positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS58" t="n">
+      <c r="BH58" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI58" t="n">
         <v>82</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="BJ58" t="n">
         <v>60</v>
       </c>
     </row>
@@ -9542,17 +12928,75 @@
         <v>73</v>
       </c>
       <c r="AQ59" t="n">
-        <v>-0.1739128631995771</v>
-      </c>
-      <c r="AR59" t="inlineStr">
+        <v>1.04</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE59" t="inlineStr">
+        <is>
+          <t>Below ₹1.01</t>
+        </is>
+      </c>
+      <c r="BF59" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG59" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS59" t="n">
+      <c r="BH59" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI59" t="n">
         <v>45</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="BJ59" t="n">
         <v>67</v>
       </c>
     </row>
@@ -9696,17 +13140,75 @@
         <v>73</v>
       </c>
       <c r="AQ60" t="n">
-        <v>-0.03648222708060733</v>
-      </c>
-      <c r="AR60" t="inlineStr">
+        <v>260.05</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>262.76</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>260.05</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>251.14</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>287.17</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE60" t="inlineStr">
+        <is>
+          <t>Below ₹251.14</t>
+        </is>
+      </c>
+      <c r="BF60" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG60" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS60" t="n">
+      <c r="BH60" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI60" t="n">
         <v>45</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="BJ60" t="n">
         <v>67</v>
       </c>
     </row>
@@ -9850,17 +13352,75 @@
         <v>73</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.2895526031949627</v>
-      </c>
-      <c r="AR61" t="inlineStr">
+        <v>339</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>345.22</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>332.77</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>357.67</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE61" t="inlineStr">
+        <is>
+          <t>Below ₹332.77</t>
+        </is>
+      </c>
+      <c r="BF61" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG61" t="inlineStr">
         <is>
           <t>Strong price trend | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS61" t="n">
+      <c r="BH61" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI61" t="n">
         <v>67</v>
       </c>
-      <c r="AT61" t="n">
+      <c r="BJ61" t="n">
         <v>67</v>
       </c>
     </row>
@@ -10004,17 +13564,75 @@
         <v>73</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.00262930156476652</v>
-      </c>
-      <c r="AR62" t="inlineStr">
+        <v>764.8200000000001</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>777.12</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>764.8200000000001</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>724.4</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>835.12</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>887.85</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE62" t="inlineStr">
+        <is>
+          <t>Below ₹724.40</t>
+        </is>
+      </c>
+      <c r="BF62" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG62" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS62" t="n">
+      <c r="BH62" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI62" t="n">
         <v>86</v>
       </c>
-      <c r="AT62" t="n">
+      <c r="BJ62" t="n">
         <v>67</v>
       </c>
     </row>
@@ -10158,17 +13776,75 @@
         <v>73</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.0694281728976802</v>
-      </c>
-      <c r="AR63" t="inlineStr">
+        <v>1142.41</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>1160.39</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>1142.41</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>1083.31</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>1245.19</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>1322.27</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>102.78</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>179.86</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE63" t="inlineStr">
+        <is>
+          <t>Below ₹1083.31</t>
+        </is>
+      </c>
+      <c r="BF63" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG63" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS63" t="n">
+      <c r="BH63" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI63" t="n">
         <v>86</v>
       </c>
-      <c r="AT63" t="n">
+      <c r="BJ63" t="n">
         <v>67</v>
       </c>
     </row>
@@ -10312,17 +13988,75 @@
         <v>72</v>
       </c>
       <c r="AQ64" t="n">
-        <v>-0.1703153251137194</v>
-      </c>
-      <c r="AR64" t="inlineStr">
+        <v>472.01</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>479.02</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>472.01</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>448.95</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>512.1</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>542.17</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE64" t="inlineStr">
+        <is>
+          <t>Below ₹448.95</t>
+        </is>
+      </c>
+      <c r="BF64" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG64" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS64" t="n">
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI64" t="n">
         <v>54</v>
       </c>
-      <c r="AT64" t="n">
+      <c r="BJ64" t="n">
         <v>90</v>
       </c>
     </row>
@@ -10466,17 +14200,75 @@
         <v>72</v>
       </c>
       <c r="AQ65" t="n">
-        <v>-0.03796168640139019</v>
-      </c>
-      <c r="AR65" t="inlineStr">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>81.65000000000001</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE65" t="inlineStr">
+        <is>
+          <t>Below ₹81.65</t>
+        </is>
+      </c>
+      <c r="BF65" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG65" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS65" t="n">
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI65" t="n">
         <v>104</v>
       </c>
-      <c r="AT65" t="n">
+      <c r="BJ65" t="n">
         <v>90</v>
       </c>
     </row>
@@ -10620,17 +14412,75 @@
         <v>72</v>
       </c>
       <c r="AQ66" t="n">
-        <v>-0.0003375054414772977</v>
-      </c>
-      <c r="AR66" t="inlineStr">
+        <v>904.21</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>920</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>904.21</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>852.36</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>994.4</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>1062.04</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>157.83</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>52W High Breakout</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>Stock is near its rolling 52-week high. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE66" t="inlineStr">
+        <is>
+          <t>Below ₹852.36</t>
+        </is>
+      </c>
+      <c r="BF66" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG66" t="inlineStr">
         <is>
           <t>Strong price trend | Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS66" t="n">
+      <c r="BH66" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI66" t="n">
         <v>104</v>
       </c>
-      <c r="AT66" t="n">
+      <c r="BJ66" t="n">
         <v>90</v>
       </c>
     </row>
@@ -10774,17 +14624,75 @@
         <v>71</v>
       </c>
       <c r="AQ67" t="n">
-        <v>-0.1468399872512514</v>
-      </c>
-      <c r="AR67" t="inlineStr">
+        <v>39.51</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>48.78</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE67" t="inlineStr">
+        <is>
+          <t>Below ₹36.46</t>
+        </is>
+      </c>
+      <c r="BF67" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG67" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS67" t="n">
+      <c r="BH67" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI67" t="n">
         <v>59</v>
       </c>
-      <c r="AT67" t="n">
+      <c r="BJ67" t="n">
         <v>98</v>
       </c>
     </row>
@@ -10928,17 +14836,75 @@
         <v>70</v>
       </c>
       <c r="AQ68" t="n">
-        <v>-0.4642858115994024</v>
-      </c>
-      <c r="AR68" t="inlineStr">
+        <v>18.25</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE68" t="inlineStr">
+        <is>
+          <t>Below ₹17.20</t>
+        </is>
+      </c>
+      <c r="BF68" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG68" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS68" t="n">
+      <c r="BH68" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI68" t="n">
         <v>67</v>
       </c>
-      <c r="AT68" t="n">
+      <c r="BJ68" t="n">
         <v>107</v>
       </c>
     </row>
@@ -11082,17 +15048,75 @@
         <v>70</v>
       </c>
       <c r="AQ69" t="n">
-        <v>-0.0448275366854716</v>
-      </c>
-      <c r="AR69" t="inlineStr">
+        <v>2058.05</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>2089.9</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>2058.05</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1953.41</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>2240.03</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>2376.52</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>104.64</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>181.99</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>318.48</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE69" t="inlineStr">
+        <is>
+          <t>Below ₹1953.41</t>
+        </is>
+      </c>
+      <c r="BF69" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG69" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Confirmed price breakout | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS69" t="n">
+      <c r="BH69" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI69" t="n">
         <v>67</v>
       </c>
-      <c r="AT69" t="n">
+      <c r="BJ69" t="n">
         <v>107</v>
       </c>
     </row>
@@ -11236,17 +15260,75 @@
         <v>70</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.09770437434124073</v>
-      </c>
-      <c r="AR70" t="inlineStr">
+        <v>437.08</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>450.01</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>445.7</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>424.16</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>475.86</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>497.41</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE70" t="inlineStr">
+        <is>
+          <t>Below ₹424.16</t>
+        </is>
+      </c>
+      <c r="BF70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG70" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS70" t="n">
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI70" t="n">
         <v>104</v>
       </c>
-      <c r="AT70" t="n">
+      <c r="BJ70" t="n">
         <v>107</v>
       </c>
     </row>
@@ -11390,17 +15472,75 @@
         <v>69</v>
       </c>
       <c r="AQ71" t="n">
-        <v>-0.03448289469789895</v>
-      </c>
-      <c r="AR71" t="inlineStr">
+        <v>26.39</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE71" t="inlineStr">
+        <is>
+          <t>Below ₹24.63</t>
+        </is>
+      </c>
+      <c r="BF71" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG71" t="inlineStr">
         <is>
           <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS71" t="n">
+      <c r="BH71" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI71" t="n">
         <v>82</v>
       </c>
-      <c r="AT71" t="n">
+      <c r="BJ71" t="n">
         <v>129</v>
       </c>
     </row>
@@ -11544,17 +15684,75 @@
         <v>69</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.1521740031827828</v>
-      </c>
-      <c r="AR72" t="inlineStr">
+        <v>289.45</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>297.93</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>295.1</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>280.97</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>314.89</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>329.02</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE72" t="inlineStr">
+        <is>
+          <t>Below ₹280.97</t>
+        </is>
+      </c>
+      <c r="BF72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG72" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Price is close to resistance | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS72" t="n">
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI72" t="n">
         <v>125</v>
       </c>
-      <c r="AT72" t="n">
+      <c r="BJ72" t="n">
         <v>129</v>
       </c>
     </row>
@@ -11696,17 +15894,75 @@
         <v>68</v>
       </c>
       <c r="AQ73" t="n">
-        <v>-0.05952375883958259</v>
-      </c>
-      <c r="AR73" t="inlineStr">
+        <v>5.29</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE73" t="inlineStr">
+        <is>
+          <t>Below ₹5.18</t>
+        </is>
+      </c>
+      <c r="BF73" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG73" t="inlineStr">
         <is>
           <t>Strong price trend | Confirmed price breakout | Volume is more than 2x average | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS73" t="n">
+      <c r="BH73" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI73" t="n">
         <v>86</v>
       </c>
-      <c r="AT73" t="n">
+      <c r="BJ73" t="n">
         <v>137</v>
       </c>
     </row>
@@ -11848,17 +16104,75 @@
         <v>68</v>
       </c>
       <c r="AQ74" t="n">
-        <v>-0.05940588450106899</v>
-      </c>
-      <c r="AR74" t="inlineStr">
+        <v>3.4</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE74" t="inlineStr">
+        <is>
+          <t>Below ₹3.33</t>
+        </is>
+      </c>
+      <c r="BF74" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG74" t="inlineStr">
         <is>
           <t>Strong price trend | Confirmed price breakout | Volume is more than 2x average | Price is above 200 DMA | Price is near 52-week high</t>
         </is>
       </c>
-      <c r="AS74" t="n">
+      <c r="BH74" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI74" t="n">
         <v>86</v>
       </c>
-      <c r="AT74" t="n">
+      <c r="BJ74" t="n">
         <v>137</v>
       </c>
     </row>
@@ -12002,17 +16316,75 @@
         <v>67</v>
       </c>
       <c r="AQ75" t="n">
-        <v>-0.1833334039758678</v>
-      </c>
-      <c r="AR75" t="inlineStr">
+        <v>17.87</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE75" t="inlineStr">
+        <is>
+          <t>Below ₹16.85</t>
+        </is>
+      </c>
+      <c r="BF75" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG75" t="inlineStr">
         <is>
           <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS75" t="n">
+      <c r="BH75" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI75" t="n">
         <v>104</v>
       </c>
-      <c r="AT75" t="n">
+      <c r="BJ75" t="n">
         <v>150</v>
       </c>
     </row>
@@ -12156,17 +16528,75 @@
         <v>66</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.01052630522244578</v>
-      </c>
-      <c r="AR76" t="inlineStr">
+        <v>5.73</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE76" t="inlineStr">
+        <is>
+          <t>Below ₹4.00</t>
+        </is>
+      </c>
+      <c r="BF76" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BG76" t="inlineStr">
         <is>
           <t>Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS76" t="n">
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI76" t="n">
         <v>125</v>
       </c>
-      <c r="AT76" t="n">
+      <c r="BJ76" t="n">
         <v>189</v>
       </c>
     </row>
@@ -12310,17 +16740,75 @@
         <v>66</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.03516907672241457</v>
-      </c>
-      <c r="AR77" t="inlineStr">
+        <v>312</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>323.88</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>317.94</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>210.05</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>366.46</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>107.89</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE77" t="inlineStr">
+        <is>
+          <t>Below ₹210.05</t>
+        </is>
+      </c>
+      <c r="BF77" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BG77" t="inlineStr">
         <is>
           <t>Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS77" t="n">
+      <c r="BH77" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI77" t="n">
         <v>125</v>
       </c>
-      <c r="AT77" t="n">
+      <c r="BJ77" t="n">
         <v>189</v>
       </c>
     </row>
@@ -12464,17 +16952,75 @@
         <v>66</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.09691453824305701</v>
-      </c>
-      <c r="AR78" t="inlineStr">
+        <v>3513.33</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>3567.15</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>3540.24</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>3280.88</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>3580.6</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>3759.99</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>259.36</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>219.75</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr">
+        <is>
+          <t>Below ₹3280.88</t>
+        </is>
+      </c>
+      <c r="BF78" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BG78" t="inlineStr">
         <is>
           <t>Positive momentum | Price is close to resistance | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS78" t="n">
+      <c r="BH78" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI78" t="n">
         <v>125</v>
       </c>
-      <c r="AT78" t="n">
+      <c r="BJ78" t="n">
         <v>189</v>
       </c>
     </row>
@@ -12618,17 +17164,75 @@
         <v>66</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.1189981823243949</v>
-      </c>
-      <c r="AR79" t="inlineStr">
+        <v>416.49</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>425.13</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>422.25</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>407.84</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>442.42</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>456.83</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>Momentum Trade</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>Positive trend and momentum. Prefer entry near current price or on a controlled pullback.</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr">
+        <is>
+          <t>Below ₹407.84</t>
+        </is>
+      </c>
+      <c r="BF79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG79" t="inlineStr">
         <is>
           <t>Price is in an uptrend | Strong positive momentum | Price is close to resistance | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS79" t="n">
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI79" t="n">
         <v>188</v>
       </c>
-      <c r="AT79" t="n">
+      <c r="BJ79" t="n">
         <v>189</v>
       </c>
     </row>
@@ -12772,17 +17376,75 @@
         <v>64</v>
       </c>
       <c r="AQ80" t="n">
-        <v>-0.056619535070456</v>
-      </c>
-      <c r="AR80" t="inlineStr">
+        <v>232.28</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>235.66</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>232.28</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>251.63</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE80" t="inlineStr">
+        <is>
+          <t>Below ₹221.15</t>
+        </is>
+      </c>
+      <c r="BF80" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG80" t="inlineStr">
         <is>
           <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS80" t="n">
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI80" t="n">
         <v>143</v>
       </c>
-      <c r="AT80" t="n">
+      <c r="BJ80" t="n">
         <v>231</v>
       </c>
     </row>
@@ -12926,17 +17588,75 @@
         <v>64</v>
       </c>
       <c r="AQ81" t="n">
-        <v>-0.1395349971922049</v>
-      </c>
-      <c r="AR81" t="inlineStr">
+        <v>33.14</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE81" t="inlineStr">
+        <is>
+          <t>Below ₹31.90</t>
+        </is>
+      </c>
+      <c r="BF81" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG81" t="inlineStr">
         <is>
           <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS81" t="n">
+      <c r="BH81" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI81" t="n">
         <v>143</v>
       </c>
-      <c r="AT81" t="n">
+      <c r="BJ81" t="n">
         <v>231</v>
       </c>
     </row>
@@ -13080,17 +17800,75 @@
         <v>63</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.01086964221142581</v>
-      </c>
-      <c r="AR82" t="inlineStr">
+        <v>14.89</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE82" t="inlineStr">
+        <is>
+          <t>Below ₹9.78</t>
+        </is>
+      </c>
+      <c r="BF82" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BG82" t="inlineStr">
         <is>
           <t>Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS82" t="n">
+      <c r="BH82" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI82" t="n">
         <v>188</v>
       </c>
-      <c r="AT82" t="n">
+      <c r="BJ82" t="n">
         <v>309</v>
       </c>
     </row>
@@ -13234,17 +18012,75 @@
         <v>63</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.06779633463827422</v>
-      </c>
-      <c r="AR83" t="inlineStr">
+        <v>415.57</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>420.52</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>415.57</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>364.88</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>430.41</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>445.26</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>200 DMA Recovery</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>Confirmation Required</t>
+        </is>
+      </c>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>Stock is recovering around the 200 DMA. Confirmation above the recovery level is preferred.</t>
+        </is>
+      </c>
+      <c r="BE83" t="inlineStr">
+        <is>
+          <t>Below ₹364.88</t>
+        </is>
+      </c>
+      <c r="BF83" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BG83" t="inlineStr">
         <is>
           <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS83" t="n">
+      <c r="BH83" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI83" t="n">
         <v>355</v>
       </c>
-      <c r="AT83" t="n">
+      <c r="BJ83" t="n">
         <v>309</v>
       </c>
     </row>
@@ -13388,17 +18224,75 @@
         <v>63</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.07665552650299168</v>
-      </c>
-      <c r="AR84" t="inlineStr">
+        <v>1039.09</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>1051.26</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>1039.09</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>974.21</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>1058.05</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>1106.75</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>64.88</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>200 DMA Recovery</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>Confirmation Required</t>
+        </is>
+      </c>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>Stock is recovering around the 200 DMA. Confirmation above the recovery level is preferred.</t>
+        </is>
+      </c>
+      <c r="BE84" t="inlineStr">
+        <is>
+          <t>Below ₹974.21</t>
+        </is>
+      </c>
+      <c r="BF84" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BG84" t="inlineStr">
         <is>
           <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is below 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
-      <c r="AS84" t="n">
+      <c r="BH84" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI84" t="n">
         <v>355</v>
       </c>
-      <c r="AT84" t="n">
+      <c r="BJ84" t="n">
         <v>309</v>
       </c>
     </row>
@@ -13542,17 +18436,75 @@
         <v>61</v>
       </c>
       <c r="AQ85" t="n">
-        <v>-0.1863489576910068</v>
-      </c>
-      <c r="AR85" t="inlineStr">
+        <v>307.72</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>312.14</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>307.72</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>293.2</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>332.98</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>351.92</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE85" t="inlineStr">
+        <is>
+          <t>Below ₹293.20</t>
+        </is>
+      </c>
+      <c r="BF85" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG85" t="inlineStr">
         <is>
           <t>Price trend is weak | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS85" t="n">
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI85" t="n">
         <v>207</v>
       </c>
-      <c r="AT85" t="n">
+      <c r="BJ85" t="n">
         <v>380</v>
       </c>
     </row>
@@ -13696,17 +18648,75 @@
         <v>61</v>
       </c>
       <c r="AQ86" t="n">
-        <v>-0.1797930339291506</v>
-      </c>
-      <c r="AR86" t="inlineStr">
+        <v>1586.55</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>1601.23</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>1586.55</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>1538.33</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>1670.42</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>1733.33</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>146.77</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE86" t="inlineStr">
+        <is>
+          <t>Below ₹1538.33</t>
+        </is>
+      </c>
+      <c r="BF86" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG86" t="inlineStr">
         <is>
           <t>Price trend is weak | Positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS86" t="n">
+      <c r="BH86" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI86" t="n">
         <v>207</v>
       </c>
-      <c r="AT86" t="n">
+      <c r="BJ86" t="n">
         <v>380</v>
       </c>
     </row>
@@ -13850,17 +18860,75 @@
         <v>60</v>
       </c>
       <c r="AQ87" t="n">
-        <v>-0.03030286391353351</v>
-      </c>
-      <c r="AR87" t="inlineStr">
+        <v>7.73</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>Breakout Confirmation</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>Confirmation Required</t>
+        </is>
+      </c>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>Price is near resistance. Wait for price and volume confirmation above resistance.</t>
+        </is>
+      </c>
+      <c r="BE87" t="inlineStr">
+        <is>
+          <t>Breakout invalid below ₹7.41</t>
+        </is>
+      </c>
+      <c r="BF87" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BG87" t="inlineStr">
         <is>
           <t>Strong positive momentum | Breakout requires volume confirmation | Volume is above average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS87" t="n">
+      <c r="BH87" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI87" t="n">
         <v>291</v>
       </c>
-      <c r="AT87" t="n">
+      <c r="BJ87" t="n">
         <v>444</v>
       </c>
     </row>
@@ -14004,17 +19072,75 @@
         <v>59</v>
       </c>
       <c r="AQ88" t="n">
-        <v>-0.1866812956215317</v>
-      </c>
-      <c r="AR88" t="inlineStr">
+        <v>195.15</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>197.73</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>195.15</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>186.68</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>209.88</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>220.93</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE88" t="inlineStr">
+        <is>
+          <t>Below ₹186.68</t>
+        </is>
+      </c>
+      <c r="BF88" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG88" t="inlineStr">
         <is>
           <t>Price trend is weak | Positive momentum | Confirmed price breakout | Strong volume confirmation | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS88" t="n">
+      <c r="BH88" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI88" t="n">
         <v>304</v>
       </c>
-      <c r="AT88" t="n">
+      <c r="BJ88" t="n">
         <v>464</v>
       </c>
     </row>
@@ -14158,17 +19284,75 @@
         <v>59</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.03846149878389341</v>
-      </c>
-      <c r="AR89" t="inlineStr">
+        <v>0.65</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE89" t="inlineStr">
+        <is>
+          <t>Below ₹0.39</t>
+        </is>
+      </c>
+      <c r="BF89" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BG89" t="inlineStr">
         <is>
           <t>Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
-      <c r="AS89" t="n">
+      <c r="BH89" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI89" t="n">
         <v>304</v>
       </c>
-      <c r="AT89" t="n">
+      <c r="BJ89" t="n">
         <v>464</v>
       </c>
     </row>
@@ -14312,17 +19496,75 @@
         <v>56</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.07161845368769387</v>
-      </c>
-      <c r="AR90" t="inlineStr">
+        <v>1519.5</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>1543.98</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>1531.74</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>1459.1</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>1550.1</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>1631.7</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>72.64</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE90" t="inlineStr">
+        <is>
+          <t>Below ₹1459.10</t>
+        </is>
+      </c>
+      <c r="BF90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BG90" t="inlineStr">
         <is>
           <t>Price trend is weak | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS90" t="n">
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI90" t="n">
         <v>445</v>
       </c>
-      <c r="AT90" t="n">
+      <c r="BJ90" t="n">
         <v>582</v>
       </c>
     </row>
@@ -14458,17 +19700,75 @@
         <v>55</v>
       </c>
       <c r="AQ91" t="n">
-        <v>-0.08198603891255578</v>
-      </c>
-      <c r="AR91" t="inlineStr">
+        <v>75.19</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>83.27</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>Strong Setup</t>
+        </is>
+      </c>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>Confirmed breakout above resistance. Entry requires breakout confirmation.</t>
+        </is>
+      </c>
+      <c r="BE91" t="inlineStr">
+        <is>
+          <t>Below ₹72.53</t>
+        </is>
+      </c>
+      <c r="BF91" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG91" t="inlineStr">
         <is>
           <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS91" t="n">
+      <c r="BH91" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="BI91" t="n">
         <v>493</v>
       </c>
-      <c r="AT91" t="n">
+      <c r="BJ91" t="n">
         <v>607</v>
       </c>
     </row>
@@ -14612,17 +19912,75 @@
         <v>53</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.2948709484160462</v>
-      </c>
-      <c r="AR92" t="inlineStr">
+        <v>12.61</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE92" t="inlineStr">
+        <is>
+          <t>Below ₹11.80</t>
+        </is>
+      </c>
+      <c r="BF92" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BG92" t="inlineStr">
         <is>
           <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS92" t="n">
+      <c r="BH92" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI92" t="n">
         <v>550</v>
       </c>
-      <c r="AT92" t="n">
+      <c r="BJ92" t="n">
         <v>651</v>
       </c>
     </row>
@@ -14766,17 +20124,75 @@
         <v>51</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.1543020713911845</v>
-      </c>
-      <c r="AR93" t="inlineStr">
+        <v>281.58</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>288.24</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>284.91</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>248.23</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>312.09</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE93" t="inlineStr">
+        <is>
+          <t>Below ₹248.23</t>
+        </is>
+      </c>
+      <c r="BF93" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BG93" t="inlineStr">
         <is>
           <t>Price trend is weak | Strong positive momentum | Price is close to resistance | Volume is more than 2x average | RSI indicates overbought conditions | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS93" t="n">
+      <c r="BH93" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI93" t="n">
         <v>603</v>
       </c>
-      <c r="AT93" t="n">
+      <c r="BJ93" t="n">
         <v>695</v>
       </c>
     </row>
@@ -14920,17 +20336,75 @@
         <v>50</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.2939121412194293</v>
-      </c>
-      <c r="AR94" t="inlineStr">
+        <v>87.3</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>88.06</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>81.13</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE94" t="inlineStr">
+        <is>
+          <t>Below ₹81.13</t>
+        </is>
+      </c>
+      <c r="BF94" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BG94" t="inlineStr">
         <is>
           <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS94" t="n">
+      <c r="BH94" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI94" t="n">
         <v>617</v>
       </c>
-      <c r="AT94" t="n">
+      <c r="BJ94" t="n">
         <v>711</v>
       </c>
     </row>
@@ -15074,17 +20548,75 @@
         <v>48</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.1784506940947997</v>
-      </c>
-      <c r="AR95" t="inlineStr">
+        <v>77.31</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>79.45999999999999</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>80</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>87.18000000000001</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>Pre-Breakout Trade</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>Price is approaching resistance. Prefer entry near the breakout zone rather than chasing price.</t>
+        </is>
+      </c>
+      <c r="BE95" t="inlineStr">
+        <is>
+          <t>Below ₹72.10</t>
+        </is>
+      </c>
+      <c r="BF95" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BG95" t="inlineStr">
         <is>
           <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
-      <c r="AS95" t="n">
+      <c r="BH95" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="BI95" t="n">
         <v>658</v>
       </c>
-      <c r="AT95" t="n">
+      <c r="BJ95" t="n">
         <v>759</v>
       </c>
     </row>
